--- a/e_commerce_forms/005_deli_order_form_for_in_store_pickup--e_commerce_forms.xlsx
+++ b/e_commerce_forms/005_deli_order_form_for_in_store_pickup--e_commerce_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -753,12 +753,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -820,12 +820,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'grilled_chicken',_'label':_'grilled_chicken'}</t>
+          <t>grilled_chicken</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Grilled Chicken', 'label': 'Grilled Chicken'}</t>
+          <t>Grilled Chicken</t>
         </is>
       </c>
     </row>
@@ -837,12 +837,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'turkey',_'label':_'turkey'}</t>
+          <t>turkey</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Turkey', 'label': 'Turkey'}</t>
+          <t>Turkey</t>
         </is>
       </c>
     </row>
@@ -854,12 +854,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'veggie',_'label':_'veggie'}</t>
+          <t>veggie</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Veggie', 'label': 'Veggie'}</t>
+          <t>Veggie</t>
         </is>
       </c>
     </row>
@@ -871,12 +871,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'tuna',_'label':_'tuna'}</t>
+          <t>tuna</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Tuna', 'label': 'Tuna'}</t>
+          <t>Tuna</t>
         </is>
       </c>
     </row>
@@ -888,12 +888,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'ham',_'label':_'ham'}</t>
+          <t>ham</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'Ham', 'label': 'Ham'}</t>
+          <t>Ham</t>
         </is>
       </c>
     </row>
@@ -905,12 +905,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'garden',_'label':_'garden'}</t>
+          <t>garden</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Garden', 'label': 'Garden'}</t>
+          <t>Garden</t>
         </is>
       </c>
     </row>
@@ -922,12 +922,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'caesar',_'label':_'caesar'}</t>
+          <t>caesar</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Caesar', 'label': 'Caesar'}</t>
+          <t>Caesar</t>
         </is>
       </c>
     </row>
@@ -939,12 +939,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'greek',_'label':_'greek'}</t>
+          <t>greek</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Greek', 'label': 'Greek'}</t>
+          <t>Greek</t>
         </is>
       </c>
     </row>
@@ -956,29 +956,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'greek',_'label':_'greek'}</t>
+          <t>spinach</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Greek', 'label': 'Greek'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>salad_choices</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>{'id':_5,_'name':_'spinach',_'label':_'spinach'}</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>{'id': 5, 'name': 'Spinach', 'label': 'Spinach'}</t>
+          <t>Spinach</t>
         </is>
       </c>
     </row>
